--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.21243025005531</v>
+        <v>6.209519915633988</v>
       </c>
       <c r="D2" t="n">
-        <v>38.18997986134616</v>
+        <v>6.205871727468751</v>
       </c>
       <c r="E2" t="n">
-        <v>14.25002076328698</v>
+        <v>2.315628374034135</v>
       </c>
       <c r="F2" t="n">
-        <v>14.9741369834026</v>
+        <v>2.433297259802923</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.6084778187453</v>
+        <v>6.761377645546111</v>
       </c>
       <c r="D3" t="n">
-        <v>34.01872416720439</v>
+        <v>5.528042677170713</v>
       </c>
       <c r="E3" t="n">
-        <v>14.25002076328698</v>
+        <v>2.315628374034135</v>
       </c>
       <c r="F3" t="n">
-        <v>14.9741369834026</v>
+        <v>2.433297259802923</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.0749444397648</v>
+        <v>5.37467847146178</v>
       </c>
       <c r="D4" t="n">
-        <v>33.04663525691838</v>
+        <v>5.370078229249237</v>
       </c>
       <c r="E4" t="n">
-        <v>14.25002076328698</v>
+        <v>2.315628374034135</v>
       </c>
       <c r="F4" t="n">
-        <v>14.9741369834026</v>
+        <v>2.433297259802923</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.20028768909854</v>
+        <v>7.020046749478514</v>
       </c>
       <c r="D5" t="n">
-        <v>43.06967721266618</v>
+        <v>6.998822547058254</v>
       </c>
       <c r="E5" t="n">
-        <v>14.25002076328698</v>
+        <v>2.315628374034135</v>
       </c>
       <c r="F5" t="n">
-        <v>14.9741369834026</v>
+        <v>2.433297259802923</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>73.57733892183843</v>
+        <v>11.95631757479875</v>
       </c>
       <c r="D6" t="n">
-        <v>73.45391159206223</v>
+        <v>11.93626063371011</v>
       </c>
       <c r="E6" t="n">
-        <v>14.25002076328698</v>
+        <v>2.315628374034135</v>
       </c>
       <c r="F6" t="n">
-        <v>14.9741369834026</v>
+        <v>2.433297259802923</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
